--- a/Aula12/cadastro_alunos.xlsx
+++ b/Aula12/cadastro_alunos.xlsx
@@ -413,69 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
           <t>nome</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>idade</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Altura</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>altura</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jonathan Oliveira</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>26</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>jonathan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
+      <c r="C2" t="n">
         <v>1.8</v>
       </c>
     </row>
